--- a/ASTquizApp/qBanks/NGN.xlsx
+++ b/ASTquizApp/qBanks/NGN.xlsx
@@ -1,15 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programDo\vs\ASTquizApp\ASTquizApp\qBanks\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA62BBE-9B81-452E-A0B2-7CA258AACF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$85</definedName>
@@ -19,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="304" count="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="304">
   <si>
     <t>Book</t>
   </si>
@@ -946,30 +950,27 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1013,12 +1014,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1028,9 +1025,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1039,59 +1034,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="15">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1192,15 +1137,73 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16" count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1238,7 +1241,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1272,6 +1275,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1306,9 +1310,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1414,7 +1419,7 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
+            <a:lightRig rig="threePt" dir="t">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
@@ -1481,28 +1486,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P85"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O85"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" hidden="1" customWidth="1" bestFit="1" width="16.570312" style="0"/>
-    <col min="2" max="2" hidden="1" customWidth="1" width="10.285156" style="0"/>
-    <col min="3" max="3" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="4" max="4" hidden="1" customWidth="1" bestFit="1" width="12.855469" style="0"/>
-    <col min="5" max="5" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="6" max="6" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="7" max="7" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="8" max="8" customWidth="1" bestFit="1" width="69.71094" style="0"/>
-    <col min="9" max="9" customWidth="1" bestFit="1" width="17.855469" style="0"/>
-    <col min="10" max="10" customWidth="1" bestFit="1" width="17.0" style="0"/>
-    <col min="11" max="11" customWidth="1" bestFit="1" width="17.140625" style="0"/>
-    <col min="12" max="12" customWidth="1" bestFit="1" width="18.425781" style="0"/>
-    <col min="13" max="13" customWidth="1" width="9.855469" style="0"/>
-    <col min="14" max="14" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="15" max="15" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="69.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" customWidth="1"/>
+    <col min="14" max="15" width="10" hidden="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:8" s="1" ht="18.75" customFormat="1">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="18.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1549,7 +1553,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="2" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="2" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A2" s="4" t="s">
         <v>301</v>
       </c>
@@ -1557,7 +1561,7 @@
         <v>300</v>
       </c>
       <c r="C2" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>12</v>
@@ -1566,7 +1570,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>14</v>
@@ -1590,13 +1594,13 @@
         <v>13</v>
       </c>
       <c r="N2" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A3" s="4" t="s">
         <v>301</v>
       </c>
@@ -1604,7 +1608,7 @@
         <v>300</v>
       </c>
       <c r="C3" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>12</v>
@@ -1613,7 +1617,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>14</v>
@@ -1637,13 +1641,13 @@
         <v>21</v>
       </c>
       <c r="N3" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="4" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A4" s="4" t="s">
         <v>301</v>
       </c>
@@ -1651,7 +1655,7 @@
         <v>300</v>
       </c>
       <c r="C4" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
@@ -1660,7 +1664,7 @@
         <v>34</v>
       </c>
       <c r="F4" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
@@ -1680,13 +1684,13 @@
         <v>302</v>
       </c>
       <c r="N4" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O4" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="5" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A5" s="4" t="s">
         <v>301</v>
       </c>
@@ -1694,7 +1698,7 @@
         <v>300</v>
       </c>
       <c r="C5" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>12</v>
@@ -1703,7 +1707,7 @@
         <v>21</v>
       </c>
       <c r="F5" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>14</v>
@@ -1727,13 +1731,13 @@
         <v>34</v>
       </c>
       <c r="N5" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O5" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="8:8" s="3" ht="53.25" customFormat="1" customHeight="1">
+    <row r="6" spans="1:15" s="3" customFormat="1" ht="53.25" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>301</v>
       </c>
@@ -1741,7 +1745,7 @@
         <v>300</v>
       </c>
       <c r="C6" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>12</v>
@@ -1750,7 +1754,7 @@
         <v>13</v>
       </c>
       <c r="F6" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -1774,13 +1778,13 @@
         <v>13</v>
       </c>
       <c r="N6" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="7" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A7" s="4" t="s">
         <v>301</v>
       </c>
@@ -1788,7 +1792,7 @@
         <v>300</v>
       </c>
       <c r="C7" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>12</v>
@@ -1797,7 +1801,7 @@
         <v>29</v>
       </c>
       <c r="F7" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>27</v>
@@ -1821,13 +1825,13 @@
         <v>29</v>
       </c>
       <c r="N7" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="8" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A8" s="4" t="s">
         <v>301</v>
       </c>
@@ -1835,7 +1839,7 @@
         <v>300</v>
       </c>
       <c r="C8" s="4">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>12</v>
@@ -1844,7 +1848,7 @@
         <v>21</v>
       </c>
       <c r="F8" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>14</v>
@@ -1868,13 +1872,13 @@
         <v>21</v>
       </c>
       <c r="N8" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="9" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A9" s="4" t="s">
         <v>301</v>
       </c>
@@ -1882,7 +1886,7 @@
         <v>300</v>
       </c>
       <c r="C9" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>12</v>
@@ -1891,7 +1895,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>27</v>
@@ -1915,13 +1919,13 @@
         <v>13</v>
       </c>
       <c r="N9" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O9" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="10" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A10" s="4" t="s">
         <v>301</v>
       </c>
@@ -1929,7 +1933,7 @@
         <v>300</v>
       </c>
       <c r="C10" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -1938,7 +1942,7 @@
         <v>29</v>
       </c>
       <c r="F10" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>27</v>
@@ -1962,13 +1966,13 @@
         <v>29</v>
       </c>
       <c r="N10" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O10" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A11" s="4" t="s">
         <v>301</v>
       </c>
@@ -1976,7 +1980,7 @@
         <v>300</v>
       </c>
       <c r="C11" s="4">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>12</v>
@@ -1985,7 +1989,7 @@
         <v>13</v>
       </c>
       <c r="F11" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>27</v>
@@ -2005,13 +2009,13 @@
         <v>302</v>
       </c>
       <c r="N11" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="12" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A12" s="4" t="s">
         <v>301</v>
       </c>
@@ -2019,7 +2023,7 @@
         <v>300</v>
       </c>
       <c r="C12" s="4">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>12</v>
@@ -2028,7 +2032,7 @@
         <v>21</v>
       </c>
       <c r="F12" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>14</v>
@@ -2052,13 +2056,13 @@
         <v>29</v>
       </c>
       <c r="N12" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O12" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="13" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A13" s="4" t="s">
         <v>301</v>
       </c>
@@ -2066,7 +2070,7 @@
         <v>300</v>
       </c>
       <c r="C13" s="4">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>12</v>
@@ -2075,7 +2079,7 @@
         <v>29</v>
       </c>
       <c r="F13" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>14</v>
@@ -2099,13 +2103,13 @@
         <v>34</v>
       </c>
       <c r="N13" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O13" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="14" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A14" s="4" t="s">
         <v>301</v>
       </c>
@@ -2113,7 +2117,7 @@
         <v>300</v>
       </c>
       <c r="C14" s="4">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>12</v>
@@ -2122,7 +2126,7 @@
         <v>34</v>
       </c>
       <c r="F14" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
@@ -2146,13 +2150,13 @@
         <v>13</v>
       </c>
       <c r="N14" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O14" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="15" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A15" s="4" t="s">
         <v>301</v>
       </c>
@@ -2160,7 +2164,7 @@
         <v>300</v>
       </c>
       <c r="C15" s="4">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>12</v>
@@ -2169,7 +2173,7 @@
         <v>29</v>
       </c>
       <c r="F15" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>14</v>
@@ -2193,13 +2197,13 @@
         <v>34</v>
       </c>
       <c r="N15" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O15" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="16" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A16" s="4" t="s">
         <v>301</v>
       </c>
@@ -2207,7 +2211,7 @@
         <v>300</v>
       </c>
       <c r="C16" s="4">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>12</v>
@@ -2216,7 +2220,7 @@
         <v>13</v>
       </c>
       <c r="F16" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>14</v>
@@ -2240,13 +2244,13 @@
         <v>13</v>
       </c>
       <c r="N16" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O16" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="17" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A17" s="4" t="s">
         <v>301</v>
       </c>
@@ -2254,7 +2258,7 @@
         <v>300</v>
       </c>
       <c r="C17" s="4">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>12</v>
@@ -2263,7 +2267,7 @@
         <v>34</v>
       </c>
       <c r="F17" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>27</v>
@@ -2283,13 +2287,13 @@
         <v>302</v>
       </c>
       <c r="N17" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O17" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="18" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A18" s="4" t="s">
         <v>301</v>
       </c>
@@ -2297,7 +2301,7 @@
         <v>300</v>
       </c>
       <c r="C18" s="4">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>12</v>
@@ -2306,7 +2310,7 @@
         <v>29</v>
       </c>
       <c r="F18" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>14</v>
@@ -2330,13 +2334,13 @@
         <v>34</v>
       </c>
       <c r="N18" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O18" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="19" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A19" s="4" t="s">
         <v>301</v>
       </c>
@@ -2344,7 +2348,7 @@
         <v>300</v>
       </c>
       <c r="C19" s="4">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>12</v>
@@ -2353,7 +2357,7 @@
         <v>21</v>
       </c>
       <c r="F19" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>14</v>
@@ -2377,13 +2381,13 @@
         <v>21</v>
       </c>
       <c r="N19" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O19" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="20" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A20" s="4" t="s">
         <v>301</v>
       </c>
@@ -2391,7 +2395,7 @@
         <v>300</v>
       </c>
       <c r="C20" s="4">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>12</v>
@@ -2400,7 +2404,7 @@
         <v>13</v>
       </c>
       <c r="F20" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>14</v>
@@ -2424,13 +2428,13 @@
         <v>34</v>
       </c>
       <c r="N20" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O20" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="21" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A21" s="4" t="s">
         <v>301</v>
       </c>
@@ -2438,7 +2442,7 @@
         <v>300</v>
       </c>
       <c r="C21" s="4">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>12</v>
@@ -2447,7 +2451,7 @@
         <v>29</v>
       </c>
       <c r="F21" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>14</v>
@@ -2456,28 +2460,28 @@
         <v>74</v>
       </c>
       <c r="I21" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K21" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L21" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>29</v>
       </c>
       <c r="N21" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O21" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="22" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A22" s="4" t="s">
         <v>301</v>
       </c>
@@ -2485,7 +2489,7 @@
         <v>300</v>
       </c>
       <c r="C22" s="4">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>12</v>
@@ -2494,7 +2498,7 @@
         <v>34</v>
       </c>
       <c r="F22" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>27</v>
@@ -2514,13 +2518,13 @@
         <v>302</v>
       </c>
       <c r="N22" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O22" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="23" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A23" s="4" t="s">
         <v>301</v>
       </c>
@@ -2528,7 +2532,7 @@
         <v>300</v>
       </c>
       <c r="C23" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>12</v>
@@ -2537,7 +2541,7 @@
         <v>29</v>
       </c>
       <c r="F23" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>14</v>
@@ -2561,13 +2565,13 @@
         <v>21</v>
       </c>
       <c r="N23" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O23" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="24" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A24" s="4" t="s">
         <v>301</v>
       </c>
@@ -2575,7 +2579,7 @@
         <v>300</v>
       </c>
       <c r="C24" s="4">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>12</v>
@@ -2584,7 +2588,7 @@
         <v>21</v>
       </c>
       <c r="F24" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>14</v>
@@ -2608,13 +2612,13 @@
         <v>34</v>
       </c>
       <c r="N24" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O24" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="25" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A25" s="4" t="s">
         <v>301</v>
       </c>
@@ -2622,7 +2626,7 @@
         <v>300</v>
       </c>
       <c r="C25" s="4">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>12</v>
@@ -2631,7 +2635,7 @@
         <v>29</v>
       </c>
       <c r="F25" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>14</v>
@@ -2655,13 +2659,13 @@
         <v>34</v>
       </c>
       <c r="N25" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="26" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A26" s="4" t="s">
         <v>301</v>
       </c>
@@ -2669,7 +2673,7 @@
         <v>300</v>
       </c>
       <c r="C26" s="4">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>12</v>
@@ -2678,7 +2682,7 @@
         <v>34</v>
       </c>
       <c r="F26" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>27</v>
@@ -2698,13 +2702,13 @@
         <v>302</v>
       </c>
       <c r="N26" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O26" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="27" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A27" s="4" t="s">
         <v>301</v>
       </c>
@@ -2712,7 +2716,7 @@
         <v>300</v>
       </c>
       <c r="C27" s="4">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>86</v>
@@ -2721,7 +2725,7 @@
         <v>29</v>
       </c>
       <c r="F27" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>14</v>
@@ -2730,28 +2734,28 @@
         <v>87</v>
       </c>
       <c r="I27" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K27" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L27" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>13</v>
       </c>
       <c r="N27" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O27" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="28" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A28" s="4" t="s">
         <v>301</v>
       </c>
@@ -2759,7 +2763,7 @@
         <v>300</v>
       </c>
       <c r="C28" s="4">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>86</v>
@@ -2768,7 +2772,7 @@
         <v>13</v>
       </c>
       <c r="F28" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>14</v>
@@ -2792,13 +2796,13 @@
         <v>21</v>
       </c>
       <c r="N28" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O28" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="29" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A29" s="4" t="s">
         <v>301</v>
       </c>
@@ -2806,7 +2810,7 @@
         <v>300</v>
       </c>
       <c r="C29" s="4">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>86</v>
@@ -2815,7 +2819,7 @@
         <v>34</v>
       </c>
       <c r="F29" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>14</v>
@@ -2839,13 +2843,13 @@
         <v>13</v>
       </c>
       <c r="N29" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O29" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="30" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A30" s="4" t="s">
         <v>301</v>
       </c>
@@ -2853,7 +2857,7 @@
         <v>300</v>
       </c>
       <c r="C30" s="4">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>86</v>
@@ -2862,7 +2866,7 @@
         <v>29</v>
       </c>
       <c r="F30" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>27</v>
@@ -2882,13 +2886,13 @@
         <v>302</v>
       </c>
       <c r="N30" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O30" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="31" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A31" s="4" t="s">
         <v>301</v>
       </c>
@@ -2896,7 +2900,7 @@
         <v>300</v>
       </c>
       <c r="C31" s="4">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>86</v>
@@ -2905,7 +2909,7 @@
         <v>34</v>
       </c>
       <c r="F31" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>14</v>
@@ -2929,13 +2933,13 @@
         <v>21</v>
       </c>
       <c r="N31" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O31" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="32" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A32" s="4" t="s">
         <v>301</v>
       </c>
@@ -2943,7 +2947,7 @@
         <v>300</v>
       </c>
       <c r="C32" s="4">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>86</v>
@@ -2952,7 +2956,7 @@
         <v>13</v>
       </c>
       <c r="F32" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>14</v>
@@ -2976,13 +2980,13 @@
         <v>21</v>
       </c>
       <c r="N32" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O32" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="33" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A33" s="4" t="s">
         <v>301</v>
       </c>
@@ -2990,7 +2994,7 @@
         <v>300</v>
       </c>
       <c r="C33" s="4">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>86</v>
@@ -2999,7 +3003,7 @@
         <v>29</v>
       </c>
       <c r="F33" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>14</v>
@@ -3023,13 +3027,13 @@
         <v>29</v>
       </c>
       <c r="N33" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O33" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="34" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A34" s="4" t="s">
         <v>301</v>
       </c>
@@ -3037,7 +3041,7 @@
         <v>300</v>
       </c>
       <c r="C34" s="4">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>86</v>
@@ -3046,7 +3050,7 @@
         <v>34</v>
       </c>
       <c r="F34" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>27</v>
@@ -3066,13 +3070,13 @@
         <v>302</v>
       </c>
       <c r="N34" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O34" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="35" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A35" s="4" t="s">
         <v>301</v>
       </c>
@@ -3080,7 +3084,7 @@
         <v>300</v>
       </c>
       <c r="C35" s="4">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>86</v>
@@ -3089,7 +3093,7 @@
         <v>29</v>
       </c>
       <c r="F35" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>14</v>
@@ -3113,13 +3117,13 @@
         <v>13</v>
       </c>
       <c r="N35" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O35" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="36" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A36" s="4" t="s">
         <v>301</v>
       </c>
@@ -3127,7 +3131,7 @@
         <v>300</v>
       </c>
       <c r="C36" s="4">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>86</v>
@@ -3136,7 +3140,7 @@
         <v>13</v>
       </c>
       <c r="F36" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>14</v>
@@ -3160,13 +3164,13 @@
         <v>29</v>
       </c>
       <c r="N36" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O36" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="37" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A37" s="4" t="s">
         <v>301</v>
       </c>
@@ -3174,7 +3178,7 @@
         <v>300</v>
       </c>
       <c r="C37" s="4">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>86</v>
@@ -3183,7 +3187,7 @@
         <v>34</v>
       </c>
       <c r="F37" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>14</v>
@@ -3207,13 +3211,13 @@
         <v>21</v>
       </c>
       <c r="N37" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O37" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="38" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A38" s="4" t="s">
         <v>301</v>
       </c>
@@ -3221,7 +3225,7 @@
         <v>300</v>
       </c>
       <c r="C38" s="4">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>86</v>
@@ -3230,7 +3234,7 @@
         <v>21</v>
       </c>
       <c r="F38" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>27</v>
@@ -3250,13 +3254,13 @@
         <v>302</v>
       </c>
       <c r="N38" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O38" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="39" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A39" s="4" t="s">
         <v>301</v>
       </c>
@@ -3264,7 +3268,7 @@
         <v>300</v>
       </c>
       <c r="C39" s="4">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>86</v>
@@ -3273,7 +3277,7 @@
         <v>29</v>
       </c>
       <c r="F39" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>14</v>
@@ -3297,13 +3301,13 @@
         <v>34</v>
       </c>
       <c r="N39" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O39" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="40" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A40" s="4" t="s">
         <v>301</v>
       </c>
@@ -3311,7 +3315,7 @@
         <v>300</v>
       </c>
       <c r="C40" s="4">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>86</v>
@@ -3320,7 +3324,7 @@
         <v>34</v>
       </c>
       <c r="F40" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>14</v>
@@ -3344,13 +3348,13 @@
         <v>13</v>
       </c>
       <c r="N40" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O40" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="41" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A41" s="4" t="s">
         <v>301</v>
       </c>
@@ -3358,7 +3362,7 @@
         <v>300</v>
       </c>
       <c r="C41" s="4">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>86</v>
@@ -3367,7 +3371,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>14</v>
@@ -3391,13 +3395,13 @@
         <v>29</v>
       </c>
       <c r="N41" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O41" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="42" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A42" s="4" t="s">
         <v>301</v>
       </c>
@@ -3405,7 +3409,7 @@
         <v>300</v>
       </c>
       <c r="C42" s="4">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>86</v>
@@ -3414,7 +3418,7 @@
         <v>21</v>
       </c>
       <c r="F42" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>14</v>
@@ -3438,13 +3442,13 @@
         <v>21</v>
       </c>
       <c r="N42" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O42" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="43" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A43" s="4" t="s">
         <v>301</v>
       </c>
@@ -3452,7 +3456,7 @@
         <v>300</v>
       </c>
       <c r="C43" s="4">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>86</v>
@@ -3461,7 +3465,7 @@
         <v>34</v>
       </c>
       <c r="F43" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>14</v>
@@ -3485,13 +3489,13 @@
         <v>13</v>
       </c>
       <c r="N43" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O43" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="44" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A44" s="4" t="s">
         <v>301</v>
       </c>
@@ -3499,7 +3503,7 @@
         <v>300</v>
       </c>
       <c r="C44" s="4">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>86</v>
@@ -3508,7 +3512,7 @@
         <v>21</v>
       </c>
       <c r="F44" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>27</v>
@@ -3528,13 +3532,13 @@
         <v>302</v>
       </c>
       <c r="N44" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O44" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="45" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A45" s="4" t="s">
         <v>301</v>
       </c>
@@ -3542,7 +3546,7 @@
         <v>300</v>
       </c>
       <c r="C45" s="4">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>136</v>
@@ -3551,7 +3555,7 @@
         <v>13</v>
       </c>
       <c r="F45" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>14</v>
@@ -3575,13 +3579,13 @@
         <v>21</v>
       </c>
       <c r="N45" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O45" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="46" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A46" s="4" t="s">
         <v>301</v>
       </c>
@@ -3589,7 +3593,7 @@
         <v>300</v>
       </c>
       <c r="C46" s="4">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>136</v>
@@ -3598,7 +3602,7 @@
         <v>21</v>
       </c>
       <c r="F46" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>14</v>
@@ -3622,13 +3626,13 @@
         <v>13</v>
       </c>
       <c r="N46" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O46" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="47" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A47" s="4" t="s">
         <v>301</v>
       </c>
@@ -3636,7 +3640,7 @@
         <v>300</v>
       </c>
       <c r="C47" s="4">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>136</v>
@@ -3645,7 +3649,7 @@
         <v>21</v>
       </c>
       <c r="F47" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>14</v>
@@ -3669,13 +3673,13 @@
         <v>34</v>
       </c>
       <c r="N47" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O47" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="48" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A48" s="4" t="s">
         <v>301</v>
       </c>
@@ -3683,7 +3687,7 @@
         <v>300</v>
       </c>
       <c r="C48" s="4">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>136</v>
@@ -3692,7 +3696,7 @@
         <v>13</v>
       </c>
       <c r="F48" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>14</v>
@@ -3716,13 +3720,13 @@
         <v>34</v>
       </c>
       <c r="N48" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O48" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="49" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A49" s="4" t="s">
         <v>301</v>
       </c>
@@ -3730,7 +3734,7 @@
         <v>300</v>
       </c>
       <c r="C49" s="4">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>136</v>
@@ -3739,7 +3743,7 @@
         <v>21</v>
       </c>
       <c r="F49" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>27</v>
@@ -3759,13 +3763,13 @@
         <v>302</v>
       </c>
       <c r="N49" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O49" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="50" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A50" s="4" t="s">
         <v>301</v>
       </c>
@@ -3773,7 +3777,7 @@
         <v>300</v>
       </c>
       <c r="C50" s="4">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>136</v>
@@ -3782,7 +3786,7 @@
         <v>13</v>
       </c>
       <c r="F50" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>27</v>
@@ -3802,13 +3806,13 @@
         <v>303</v>
       </c>
       <c r="N50" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O50" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="51" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A51" s="4" t="s">
         <v>301</v>
       </c>
@@ -3816,7 +3820,7 @@
         <v>300</v>
       </c>
       <c r="C51" s="4">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>136</v>
@@ -3825,7 +3829,7 @@
         <v>21</v>
       </c>
       <c r="F51" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>27</v>
@@ -3845,13 +3849,13 @@
         <v>302</v>
       </c>
       <c r="N51" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O51" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="52" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A52" s="4" t="s">
         <v>301</v>
       </c>
@@ -3859,7 +3863,7 @@
         <v>300</v>
       </c>
       <c r="C52" s="4">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>156</v>
@@ -3868,7 +3872,7 @@
         <v>13</v>
       </c>
       <c r="F52" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>14</v>
@@ -3892,13 +3896,13 @@
         <v>13</v>
       </c>
       <c r="N52" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O52" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="53" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A53" s="4" t="s">
         <v>301</v>
       </c>
@@ -3906,7 +3910,7 @@
         <v>300</v>
       </c>
       <c r="C53" s="4">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>156</v>
@@ -3915,7 +3919,7 @@
         <v>34</v>
       </c>
       <c r="F53" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>14</v>
@@ -3939,13 +3943,13 @@
         <v>21</v>
       </c>
       <c r="N53" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O53" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="54" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A54" s="4" t="s">
         <v>301</v>
       </c>
@@ -3953,7 +3957,7 @@
         <v>300</v>
       </c>
       <c r="C54" s="4">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>156</v>
@@ -3962,7 +3966,7 @@
         <v>13</v>
       </c>
       <c r="F54" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>14</v>
@@ -3986,13 +3990,13 @@
         <v>29</v>
       </c>
       <c r="N54" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O54" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="55" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A55" s="4" t="s">
         <v>301</v>
       </c>
@@ -4000,7 +4004,7 @@
         <v>300</v>
       </c>
       <c r="C55" s="4">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>156</v>
@@ -4009,7 +4013,7 @@
         <v>21</v>
       </c>
       <c r="F55" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>14</v>
@@ -4033,13 +4037,13 @@
         <v>34</v>
       </c>
       <c r="N55" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O55" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="56" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A56" s="4" t="s">
         <v>301</v>
       </c>
@@ -4047,7 +4051,7 @@
         <v>300</v>
       </c>
       <c r="C56" s="4">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>156</v>
@@ -4056,7 +4060,7 @@
         <v>21</v>
       </c>
       <c r="F56" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>14</v>
@@ -4080,13 +4084,13 @@
         <v>21</v>
       </c>
       <c r="N56" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O56" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="8:8" s="3" ht="75.0" customFormat="1">
+    <row r="57" spans="1:15" s="3" customFormat="1" ht="75">
       <c r="A57" s="4" t="s">
         <v>301</v>
       </c>
@@ -4094,7 +4098,7 @@
         <v>300</v>
       </c>
       <c r="C57" s="4">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>156</v>
@@ -4103,7 +4107,7 @@
         <v>13</v>
       </c>
       <c r="F57" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>14</v>
@@ -4127,13 +4131,13 @@
         <v>29</v>
       </c>
       <c r="N57" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O57" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="58" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A58" s="4" t="s">
         <v>301</v>
       </c>
@@ -4141,7 +4145,7 @@
         <v>300</v>
       </c>
       <c r="C58" s="4">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>156</v>
@@ -4150,7 +4154,7 @@
         <v>21</v>
       </c>
       <c r="F58" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>14</v>
@@ -4174,13 +4178,13 @@
         <v>13</v>
       </c>
       <c r="N58" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O58" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="59" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A59" s="4" t="s">
         <v>301</v>
       </c>
@@ -4188,7 +4192,7 @@
         <v>300</v>
       </c>
       <c r="C59" s="4">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>156</v>
@@ -4197,7 +4201,7 @@
         <v>21</v>
       </c>
       <c r="F59" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>14</v>
@@ -4221,13 +4225,13 @@
         <v>21</v>
       </c>
       <c r="N59" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O59" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="60" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A60" s="4" t="s">
         <v>301</v>
       </c>
@@ -4235,7 +4239,7 @@
         <v>300</v>
       </c>
       <c r="C60" s="4">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>156</v>
@@ -4244,7 +4248,7 @@
         <v>13</v>
       </c>
       <c r="F60" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>14</v>
@@ -4268,13 +4272,13 @@
         <v>29</v>
       </c>
       <c r="N60" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O60" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="61" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A61" s="4" t="s">
         <v>301</v>
       </c>
@@ -4282,7 +4286,7 @@
         <v>300</v>
       </c>
       <c r="C61" s="4">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>156</v>
@@ -4291,7 +4295,7 @@
         <v>21</v>
       </c>
       <c r="F61" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>14</v>
@@ -4315,13 +4319,13 @@
         <v>21</v>
       </c>
       <c r="N61" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O61" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="62" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A62" s="4" t="s">
         <v>301</v>
       </c>
@@ -4329,7 +4333,7 @@
         <v>300</v>
       </c>
       <c r="C62" s="4">
-        <v>61.0</v>
+        <v>61</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>156</v>
@@ -4338,7 +4342,7 @@
         <v>13</v>
       </c>
       <c r="F62" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>14</v>
@@ -4362,13 +4366,13 @@
         <v>29</v>
       </c>
       <c r="N62" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O62" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="63" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A63" s="4" t="s">
         <v>301</v>
       </c>
@@ -4376,7 +4380,7 @@
         <v>300</v>
       </c>
       <c r="C63" s="4">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>156</v>
@@ -4385,7 +4389,7 @@
         <v>21</v>
       </c>
       <c r="F63" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>14</v>
@@ -4409,13 +4413,13 @@
         <v>34</v>
       </c>
       <c r="N63" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O63" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="64" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A64" s="4" t="s">
         <v>301</v>
       </c>
@@ -4423,7 +4427,7 @@
         <v>300</v>
       </c>
       <c r="C64" s="4">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>156</v>
@@ -4432,7 +4436,7 @@
         <v>13</v>
       </c>
       <c r="F64" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>14</v>
@@ -4456,13 +4460,13 @@
         <v>21</v>
       </c>
       <c r="N64" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O64" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="65" spans="1:15" s="3" customFormat="1" ht="60">
       <c r="A65" s="4" t="s">
         <v>301</v>
       </c>
@@ -4470,7 +4474,7 @@
         <v>300</v>
       </c>
       <c r="C65" s="4">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>156</v>
@@ -4479,7 +4483,7 @@
         <v>13</v>
       </c>
       <c r="F65" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>27</v>
@@ -4499,13 +4503,13 @@
         <v>302</v>
       </c>
       <c r="N65" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O65" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="66" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A66" s="4" t="s">
         <v>301</v>
       </c>
@@ -4513,7 +4517,7 @@
         <v>300</v>
       </c>
       <c r="C66" s="4">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>218</v>
@@ -4522,7 +4526,7 @@
         <v>29</v>
       </c>
       <c r="F66" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>14</v>
@@ -4546,13 +4550,13 @@
         <v>29</v>
       </c>
       <c r="N66" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O66" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="67" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="67" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A67" s="4" t="s">
         <v>301</v>
       </c>
@@ -4560,7 +4564,7 @@
         <v>300</v>
       </c>
       <c r="C67" s="4">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>218</v>
@@ -4569,7 +4573,7 @@
         <v>21</v>
       </c>
       <c r="F67" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G67" s="7" t="s">
         <v>27</v>
@@ -4589,13 +4593,13 @@
         <v>302</v>
       </c>
       <c r="N67" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O67" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="68" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="68" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A68" s="4" t="s">
         <v>301</v>
       </c>
@@ -4603,7 +4607,7 @@
         <v>300</v>
       </c>
       <c r="C68" s="4">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>218</v>
@@ -4612,7 +4616,7 @@
         <v>34</v>
       </c>
       <c r="F68" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G68" s="7" t="s">
         <v>14</v>
@@ -4636,13 +4640,13 @@
         <v>29</v>
       </c>
       <c r="N68" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O68" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="69" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="69" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A69" s="4" t="s">
         <v>301</v>
       </c>
@@ -4650,7 +4654,7 @@
         <v>300</v>
       </c>
       <c r="C69" s="4">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>218</v>
@@ -4659,7 +4663,7 @@
         <v>13</v>
       </c>
       <c r="F69" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G69" s="7" t="s">
         <v>14</v>
@@ -4683,13 +4687,13 @@
         <v>21</v>
       </c>
       <c r="N69" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O69" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="70" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="70" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A70" s="4" t="s">
         <v>301</v>
       </c>
@@ -4697,7 +4701,7 @@
         <v>300</v>
       </c>
       <c r="C70" s="4">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>218</v>
@@ -4706,7 +4710,7 @@
         <v>21</v>
       </c>
       <c r="F70" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>14</v>
@@ -4730,13 +4734,13 @@
         <v>34</v>
       </c>
       <c r="N70" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O70" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="71" spans="8:8" s="6" ht="71.25" customFormat="1">
+    <row r="71" spans="1:15" s="6" customFormat="1" ht="71.25">
       <c r="A71" s="4" t="s">
         <v>301</v>
       </c>
@@ -4744,7 +4748,7 @@
         <v>300</v>
       </c>
       <c r="C71" s="4">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>239</v>
@@ -4753,7 +4757,7 @@
         <v>29</v>
       </c>
       <c r="F71" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>27</v>
@@ -4773,13 +4777,13 @@
         <v>303</v>
       </c>
       <c r="N71" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O71" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="72" spans="8:8" s="6" ht="71.25" customFormat="1">
+    <row r="72" spans="1:15" s="6" customFormat="1" ht="71.25">
       <c r="A72" s="4" t="s">
         <v>301</v>
       </c>
@@ -4787,7 +4791,7 @@
         <v>300</v>
       </c>
       <c r="C72" s="4">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>239</v>
@@ -4796,7 +4800,7 @@
         <v>13</v>
       </c>
       <c r="F72" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G72" s="7" t="s">
         <v>14</v>
@@ -4820,13 +4824,13 @@
         <v>29</v>
       </c>
       <c r="N72" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O72" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="73" spans="8:8" s="6" ht="71.25" customFormat="1">
+    <row r="73" spans="1:15" s="6" customFormat="1" ht="71.25">
       <c r="A73" s="4" t="s">
         <v>301</v>
       </c>
@@ -4834,7 +4838,7 @@
         <v>300</v>
       </c>
       <c r="C73" s="4">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="D73" s="7" t="s">
         <v>239</v>
@@ -4843,7 +4847,7 @@
         <v>34</v>
       </c>
       <c r="F73" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="7" t="s">
         <v>14</v>
@@ -4867,13 +4871,13 @@
         <v>13</v>
       </c>
       <c r="N73" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O73" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="74" spans="8:8" s="6" ht="71.25" customFormat="1">
+    <row r="74" spans="1:15" s="6" customFormat="1" ht="71.25">
       <c r="A74" s="4" t="s">
         <v>301</v>
       </c>
@@ -4881,7 +4885,7 @@
         <v>300</v>
       </c>
       <c r="C74" s="4">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>239</v>
@@ -4890,7 +4894,7 @@
         <v>21</v>
       </c>
       <c r="F74" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G74" s="7" t="s">
         <v>14</v>
@@ -4914,13 +4918,13 @@
         <v>34</v>
       </c>
       <c r="N74" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O74" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="8:8" s="6" ht="71.25" customFormat="1">
+    <row r="75" spans="1:15" s="6" customFormat="1" ht="71.25">
       <c r="A75" s="4" t="s">
         <v>301</v>
       </c>
@@ -4928,7 +4932,7 @@
         <v>300</v>
       </c>
       <c r="C75" s="4">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>239</v>
@@ -4937,7 +4941,7 @@
         <v>29</v>
       </c>
       <c r="F75" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G75" s="7" t="s">
         <v>14</v>
@@ -4961,13 +4965,13 @@
         <v>21</v>
       </c>
       <c r="N75" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O75" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="76" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="76" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A76" s="4" t="s">
         <v>301</v>
       </c>
@@ -4975,7 +4979,7 @@
         <v>300</v>
       </c>
       <c r="C76" s="4">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="D76" s="7" t="s">
         <v>261</v>
@@ -4984,7 +4988,7 @@
         <v>13</v>
       </c>
       <c r="F76" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G76" s="7" t="s">
         <v>27</v>
@@ -5004,13 +5008,13 @@
         <v>302</v>
       </c>
       <c r="N76" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O76" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="77" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="77" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A77" s="4" t="s">
         <v>301</v>
       </c>
@@ -5018,7 +5022,7 @@
         <v>300</v>
       </c>
       <c r="C77" s="4">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>261</v>
@@ -5027,7 +5031,7 @@
         <v>21</v>
       </c>
       <c r="F77" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G77" s="7" t="s">
         <v>14</v>
@@ -5051,13 +5055,13 @@
         <v>21</v>
       </c>
       <c r="N77" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O77" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="78" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="78" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A78" s="4" t="s">
         <v>301</v>
       </c>
@@ -5065,7 +5069,7 @@
         <v>300</v>
       </c>
       <c r="C78" s="4">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>268</v>
@@ -5074,7 +5078,7 @@
         <v>29</v>
       </c>
       <c r="F78" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>14</v>
@@ -5098,13 +5102,13 @@
         <v>13</v>
       </c>
       <c r="N78" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O78" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="79" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="79" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A79" s="4" t="s">
         <v>301</v>
       </c>
@@ -5112,7 +5116,7 @@
         <v>300</v>
       </c>
       <c r="C79" s="4">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>268</v>
@@ -5121,7 +5125,7 @@
         <v>13</v>
       </c>
       <c r="F79" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>14</v>
@@ -5145,13 +5149,13 @@
         <v>29</v>
       </c>
       <c r="N79" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O79" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="80" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="80" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A80" s="4" t="s">
         <v>301</v>
       </c>
@@ -5159,7 +5163,7 @@
         <v>300</v>
       </c>
       <c r="C80" s="4">
-        <v>79.0</v>
+        <v>79</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>268</v>
@@ -5168,7 +5172,7 @@
         <v>34</v>
       </c>
       <c r="F80" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="7" t="s">
         <v>14</v>
@@ -5192,13 +5196,13 @@
         <v>34</v>
       </c>
       <c r="N80" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O80" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="81" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="81" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A81" s="4" t="s">
         <v>301</v>
       </c>
@@ -5206,7 +5210,7 @@
         <v>300</v>
       </c>
       <c r="C81" s="4">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>281</v>
@@ -5215,7 +5219,7 @@
         <v>21</v>
       </c>
       <c r="F81" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>14</v>
@@ -5239,13 +5243,13 @@
         <v>34</v>
       </c>
       <c r="N81" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O81" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="82" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="82" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A82" s="4" t="s">
         <v>301</v>
       </c>
@@ -5253,7 +5257,7 @@
         <v>300</v>
       </c>
       <c r="C82" s="4">
-        <v>81.0</v>
+        <v>81</v>
       </c>
       <c r="D82" s="7" t="s">
         <v>281</v>
@@ -5262,7 +5266,7 @@
         <v>13</v>
       </c>
       <c r="F82" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>27</v>
@@ -5282,13 +5286,13 @@
         <v>302</v>
       </c>
       <c r="N82" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O82" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="83" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="83" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A83" s="4" t="s">
         <v>301</v>
       </c>
@@ -5296,7 +5300,7 @@
         <v>300</v>
       </c>
       <c r="C83" s="4">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>288</v>
@@ -5305,7 +5309,7 @@
         <v>13</v>
       </c>
       <c r="F83" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G83" s="7" t="s">
         <v>27</v>
@@ -5325,13 +5329,13 @@
         <v>302</v>
       </c>
       <c r="N83" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O83" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="84" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="84" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A84" s="4" t="s">
         <v>301</v>
       </c>
@@ -5339,7 +5343,7 @@
         <v>300</v>
       </c>
       <c r="C84" s="4">
-        <v>83.0</v>
+        <v>83</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>288</v>
@@ -5348,7 +5352,7 @@
         <v>34</v>
       </c>
       <c r="F84" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G84" s="7" t="s">
         <v>14</v>
@@ -5372,13 +5376,13 @@
         <v>21</v>
       </c>
       <c r="N84" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O84" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="85" spans="8:8" s="6" ht="60.0" customFormat="1">
+    <row r="85" spans="1:15" s="6" customFormat="1" ht="60">
       <c r="A85" s="4" t="s">
         <v>301</v>
       </c>
@@ -5386,7 +5390,7 @@
         <v>300</v>
       </c>
       <c r="C85" s="4">
-        <v>84.0</v>
+        <v>84</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>288</v>
@@ -5395,7 +5399,7 @@
         <v>21</v>
       </c>
       <c r="F85" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>14</v>
@@ -5419,7 +5423,7 @@
         <v>21</v>
       </c>
       <c r="N85" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O85" s="7" t="s">
         <v>224</v>
@@ -5427,56 +5431,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H56">
-    <cfRule type="duplicateValues" priority="7" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="6" dxfId="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="duplicateValues" priority="4" dxfId="2"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="3"/>
-    <cfRule type="duplicateValues" priority="1" dxfId="4"/>
-    <cfRule type="duplicateValues" priority="3" dxfId="5"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51">
-    <cfRule type="duplicateValues" priority="10" dxfId="6"/>
-    <cfRule type="duplicateValues" priority="11" dxfId="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H53:H65">
-    <cfRule type="duplicateValues" priority="5" dxfId="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H52">
-    <cfRule type="duplicateValues" priority="8" dxfId="9"/>
-    <cfRule type="duplicateValues" priority="9" dxfId="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H46:H51">
-    <cfRule type="duplicateValues" priority="13" dxfId="11"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H65">
-    <cfRule type="duplicateValues" priority="12" dxfId="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H43:H51">
-    <cfRule type="duplicateValues" priority="14" dxfId="13"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H52 H56:H65">
-    <cfRule type="duplicateValues" priority="15" dxfId="14"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>